--- a/resultados_cluster/evaluated_metrics_summary.xlsx
+++ b/resultados_cluster/evaluated_metrics_summary.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -533,22 +533,22 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.9757 ± 0.0229</t>
+          <t>0.9784 ± 0.0229</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0.7277 ± 0.1475</t>
+          <t>0.7470 ± 0.0165</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0.6075 ± 0.0295</t>
+          <t>0.8201 ± 0.0854</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0.7199 ± 0.0329</t>
+          <t>0.9932 ± 0.0053</t>
         </is>
       </c>
     </row>
@@ -600,17 +600,17 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0.8590 ± 0.0093</t>
+          <t>0.8123 ± 0.0207</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0.6862 ± 0.0160</t>
+          <t>0.8386 ± 0.0939</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0.8485 ± 0.0564</t>
+          <t>0.9893 ± 0.0160</t>
         </is>
       </c>
     </row>
@@ -657,49 +657,49 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.8882 ± 0.0299</t>
+          <t>0.8991 ± 0.0427</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0.7826 ± 0.0139</t>
+          <t>0.7030 ± 0.0234</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0.6493 ± 0.0177</t>
+          <t>0.8690 ± 0.0749</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0.7153 ± 0.0175</t>
+          <t>0.9894 ± 0.0134</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MAAL</t>
+          <t>baseline</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.9926 ± 0.0023</t>
+          <t>0.9931 ± 0.0024</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.9945 ± 0.0017</t>
+          <t>0.9949 ± 0.0018</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.9908 ± 0.0027</t>
+          <t>0.9915 ± 0.0025</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.9981 ± 0.0017</t>
+          <t>0.9983 ± 0.0012</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -719,49 +719,49 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.2339 ± 0.1298</t>
+          <t>0.1757 ± 0.0313</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0.0635 ± 0.0161</t>
+          <t>0.0381 ± 0.0168</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0.6863 ± 0.0791</t>
+          <t>0.7286 ± 0.1254</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0.7359 ± 0.0894</t>
+          <t>0.8879 ± 0.0897</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>MAAL</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0.9931 ± 0.0024</t>
+          <t>0.9564 ± 0.0723</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.9949 ± 0.0018</t>
+          <t>0.9635 ± 0.0629</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.9915 ± 0.0025</t>
+          <t>0.9926 ± 0.0032</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.9983 ± 0.0012</t>
+          <t>0.9419 ± 0.1117</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -781,146 +781,332 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.1728 ± 0.0290</t>
+          <t>0.1748 ± 0.2931</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>0.0254 ± 0.0115</t>
+          <t>0.0329 ± 0.0465</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>0.5717 ± 0.0502</t>
+          <t>0.8432 ± 0.1484</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0.6676 ± 0.0209</t>
+          <t>0.7284 ± 0.1449</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>MAAL_V4</t>
+          <t>MAAL_V7</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0.8589 ± 0.1681</t>
+          <t>0.9854 ± 0.0021</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.9141 ± 0.0991</t>
+          <t>0.9891 ± 0.0015</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.8558 ± 0.1656</t>
+          <t>0.9904 ± 0.0014</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.9977 ± 0.0023</t>
+          <t>0.9878 ± 0.0019</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0.8554 ± 0.0084</t>
+          <t>0.8567 ± 0.0061</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0.9034 ± 0.0075</t>
+          <t>0.9042 ± 0.0056</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.9899 ± 0.0015</t>
+          <t>0.9898 ± 0.0015</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.9821 ± 0.0245</t>
+          <t>0.9910 ± 0.0083</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.8213 ± 0.0248</t>
+          <t>0.7889 ± 0.0251</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0.6285 ± 0.0330</t>
+          <t>0.7750 ± 0.1305</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0.7705 ± 0.0100</t>
+          <t>0.9822 ± 0.0209</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>MAAL_V5</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>0.9861 ± 0.0034</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>0.9897 ± 0.0025</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>0.9919 ± 0.0013</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0.9875 ± 0.0054</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0.8561 ± 0.0060</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0.9036 ± 0.0058</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0.9899 ± 0.0014</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>0.9908 ± 0.0135</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>0.7690 ± 0.0308</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0.7097 ± 0.1456</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>0.9749 ± 0.0242</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>MAAL_V6</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>0.9840 ± 0.0024</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>0.9881 ± 0.0018</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>0.9900 ± 0.0013</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0.9862 ± 0.0029</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>0.8558 ± 0.0067</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0.9034 ± 0.0063</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0.9899 ± 0.0014</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>0.9880 ± 0.0125</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>0.7543 ± 0.0278</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0.8554 ± 0.1352</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>0.9865 ± 0.0132</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>MAAL_V4</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>0.9851 ± 0.0024</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>0.9889 ± 0.0017</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>0.9910 ± 0.0028</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0.9868 ± 0.0042</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>0.8554 ± 0.0084</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0.9034 ± 0.0075</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0.9899 ± 0.0015</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>0.9908 ± 0.0084</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>0.7560 ± 0.0371</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0.7869 ± 0.0579</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>0.9871 ± 0.0036</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>MAAL_V3</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>0.9838 ± 0.0032</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>0.9879 ± 0.0023</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>0.9906 ± 0.0020</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>0.9852 ± 0.0039</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>0.8533 ± 0.0064</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>0.9014 ± 0.0062</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>0.9897 ± 0.0014</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>0.9760 ± 0.0227</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>0.4830 ± 0.0198</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>0.6346 ± 0.0370</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>0.7277 ± 0.0623</t>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>0.9847 ± 0.0107</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>0.7424 ± 0.0422</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0.8723 ± 0.1070</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>0.9921 ± 0.0087</t>
         </is>
       </c>
     </row>

--- a/resultados_cluster/evaluated_metrics_summary.xlsx
+++ b/resultados_cluster/evaluated_metrics_summary.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,62 +417,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Experiment</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Accuracy</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>F1-Score</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Precision</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Recall</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>IoU</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Dice</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Pixel Accuracy</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Pointing Game</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Saliency IoU</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Deletion Score (AUC)</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Insertion Score (AUC)</t>
         </is>
@@ -555,7 +543,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Fusion_CAM</t>
+          <t>MAAL</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -741,7 +729,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>MAAL</t>
+          <t>MAAL_V2</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
